--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-los-lagos.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2324-1056-CM26</t>
+          <t>2289-14-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,1543 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>32413.61</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2660-20-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.230.100-5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANCUD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>19839.13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1037-30-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>36986.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1426102-78-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Comercial Motores de los Andes SpA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>27447.31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2324-512-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DERCOMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>96.545.450-0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>41129.86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1095-21-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>35180.58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1095-22-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SKC Transportes S.A.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.176.602-3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>125218.09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2297-802-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>78539.34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2289-573-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.220.700-9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>71932.64999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5413-512-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>70.772.100-6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>33776.67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2289-622-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.220.700-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Comercial Motores de los Andes SpA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>25085.62</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4318-23-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.230.500-0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHONCHI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>21630.57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2904-606-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.252.200-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HUALAIHUE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>32712.79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3479-1107-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>69.220.600-2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>34813.04</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2989-467-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.220.800-5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>30631.76</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1388974-145-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>71.146.000-4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>34130.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2297-1138-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.210.100-6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>10637.64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2852-754-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>22045.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2324-1259-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>18523.11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3888-456-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.251.800-4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>37855.57</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1002-409-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>34923.02</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3723-219-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.230.800-k</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUQUELDON</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>72327.34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1002-453-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>154173.32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1002-452-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>149680.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4180-159-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>61.979.300-5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>POMPEYO CARRASCO SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>23337.98</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2324-1056-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
         <v>44713.44</v>
       </c>
     </row>
